--- a/scripts/samples/literag-项目成本.xlsx
+++ b/scripts/samples/literag-项目成本.xlsx
@@ -468,7 +468,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ChromaDB 存储</t>
+          <t>Qdrant 向量库节点</t>
         </is>
       </c>
       <c r="B3" t="n">
